--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -1149,7 +1149,7 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H6">
         <v>-1</v>
@@ -1203,7 +1203,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1226,7 +1226,7 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
         <v>-1</v>
@@ -1280,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1534,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1588,7 +1588,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1611,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1665,7 +1665,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1688,7 +1688,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1765,7 +1765,7 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1819,7 +1819,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2381,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>-1</v>
@@ -2435,7 +2435,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2458,7 +2458,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2512,7 +2512,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2535,7 +2535,7 @@
         <v>10</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2589,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2766,7 +2766,7 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H27">
         <v>-1</v>
@@ -2820,7 +2820,7 @@
         <v>6</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2920,7 +2920,7 @@
         <v>10</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2974,7 +2974,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3074,7 +3074,7 @@
         <v>7</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H31">
         <v>-1</v>
@@ -3128,7 +3128,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3151,7 +3151,7 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3205,7 +3205,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3228,7 +3228,7 @@
         <v>10</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>-1</v>
@@ -3282,7 +3282,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3459,7 +3459,7 @@
         <v>10</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3513,7 +3513,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3992,22 +3992,25 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>39.47</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>8.6</v>
+      </c>
       <c r="I3">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>60.53</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4145,7 +4148,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4234,22 +4237,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920005</v>
+        <v>19330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4266,44 +4269,44 @@
         <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920004</v>
+        <v>19330051920006</v>
       </c>
       <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>125</v>
-      </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920006</v>
+        <v>19330051920417</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4314,22 +4317,22 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920006</v>
+        <v>19330051920417</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4346,10 +4349,10 @@
         <v>126</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4366,10 +4369,10 @@
         <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4386,50 +4389,50 @@
         <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4446,10 +4449,10 @@
         <v>127</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4466,64 +4469,64 @@
         <v>127</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920007</v>
+        <v>19330051920008</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920007</v>
+        <v>19330051920008</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920008</v>
+        <v>19330051920014</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -4534,16 +4537,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920008</v>
+        <v>19330051920014</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -4566,64 +4569,64 @@
         <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920014</v>
+        <v>19330051920016</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920014</v>
+        <v>19330051920016</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920016</v>
+        <v>19330051920015</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -4634,16 +4637,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920016</v>
+        <v>19330051920015</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -4654,16 +4657,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920015</v>
+        <v>19330051920012</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -4674,36 +4677,36 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920015</v>
+        <v>19330051920011</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920012</v>
+        <v>19330051920009</v>
       </c>
       <c r="B28" t="s">
         <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -4714,36 +4717,36 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920012</v>
+        <v>19330051920010</v>
       </c>
       <c r="B29" t="s">
         <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920011</v>
+        <v>19330051920017</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -4754,16 +4757,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920011</v>
+        <v>19330051920017</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -4774,16 +4777,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920009</v>
+        <v>19330051920018</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -4794,16 +4797,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920009</v>
+        <v>19330051920018</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -4814,16 +4817,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920010</v>
+        <v>18330051920168</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -4834,16 +4837,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920010</v>
+        <v>18330051920168</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -4854,16 +4857,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920017</v>
+        <v>19330051920422</v>
       </c>
       <c r="B36" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" t="s">
         <v>80</v>
       </c>
-      <c r="C36" t="s">
-        <v>111</v>
-      </c>
       <c r="D36" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
@@ -4874,16 +4877,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920017</v>
+        <v>19330051920422</v>
       </c>
       <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
         <v>80</v>
       </c>
-      <c r="C37" t="s">
-        <v>111</v>
-      </c>
       <c r="D37" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -4894,56 +4897,56 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920018</v>
+        <v>19330051920422</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920018</v>
+        <v>19330051920422</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>18330051920168</v>
+        <v>19330051920020</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
         <v>6</v>
@@ -4954,36 +4957,36 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>18330051920168</v>
+        <v>19330051920022</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920422</v>
+        <v>19330051920021</v>
       </c>
       <c r="B42" t="s">
         <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
@@ -4994,116 +4997,116 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>19330051920422</v>
+        <v>19330051920023</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="D43" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920422</v>
+        <v>19330051920023</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>19330051920422</v>
+        <v>19330051920026</v>
       </c>
       <c r="B45" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>19330051920020</v>
+        <v>19330051920026</v>
       </c>
       <c r="B46" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>19330051920020</v>
+        <v>18330061460390</v>
       </c>
       <c r="B47" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="D47" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>19330051920022</v>
+        <v>19330051920025</v>
       </c>
       <c r="B48" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
         <v>6</v>
@@ -5114,156 +5117,156 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>19330051920022</v>
+        <v>19330051920027</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D49" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>19330051920021</v>
+        <v>19330051920024</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>19330051920023</v>
+        <v>19330051920024</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D52" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E52" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>19330051920023</v>
+        <v>19330051920024</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D53" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>19330051920026</v>
+        <v>19330051920024</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E54" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>19330051920026</v>
+        <v>19330051920029</v>
       </c>
       <c r="B55" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D55" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>18330061460390</v>
+        <v>19330051920030</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E56" t="s">
         <v>6</v>
@@ -5274,56 +5277,56 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>18330061460390</v>
+        <v>19330051920032</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D57" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>19330051920025</v>
+        <v>19330051920032</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>19330051920025</v>
+        <v>19330051920032</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -5334,56 +5337,56 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>19330051920027</v>
+        <v>19330051920032</v>
       </c>
       <c r="B60" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C60" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>19330051920027</v>
+        <v>19330051920031</v>
       </c>
       <c r="B61" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C61" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>19330051920024</v>
+        <v>19330051920035</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E62" t="s">
         <v>6</v>
@@ -5394,76 +5397,76 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>19330051920024</v>
+        <v>19330051920034</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
         <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>19330051920024</v>
+        <v>19330051920034</v>
       </c>
       <c r="B64" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
         <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>19330051920024</v>
+        <v>19330051920034</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
         <v>117</v>
       </c>
       <c r="D65" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E65" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>19330051920029</v>
+        <v>19330051920038</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C66" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D66" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E66" t="s">
         <v>6</v>
@@ -5474,16 +5477,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>19330051920029</v>
+        <v>19330051920038</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D67" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -5494,16 +5497,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>19330051920030</v>
+        <v>19330051920037</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E68" t="s">
         <v>6</v>
@@ -5514,156 +5517,156 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>19330051920030</v>
+        <v>19330051920037</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C69" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D69" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F69" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>19330051920032</v>
+        <v>19330051920037</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>19330051920032</v>
+        <v>19330051920036</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C71" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D71" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E71" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F71" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>19330051920032</v>
+        <v>19330051920036</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D72" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>19330051920032</v>
+        <v>19330051920036</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C73" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="D73" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E73" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>19330051920031</v>
+        <v>19330051920036</v>
       </c>
       <c r="B74" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="D74" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F74" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>19330051920031</v>
+        <v>19330051920036</v>
       </c>
       <c r="B75" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C75" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>19330051920035</v>
+        <v>19330051920039</v>
       </c>
       <c r="B76" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D76" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E76" t="s">
         <v>6</v>
@@ -5674,16 +5677,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>19330051920035</v>
+        <v>19330051920039</v>
       </c>
       <c r="B77" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D77" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -5694,381 +5697,81 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>19330051920034</v>
+        <v>19330051920039</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C78" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D78" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E78" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>19330051920034</v>
+        <v>19330051920040</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D79" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E79" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F79" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>19330051920034</v>
+        <v>19330051920040</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C80" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D80" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F80" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>19330051920038</v>
+        <v>19330051920040</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C81" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D81" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="E81" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F81" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>19330051920038</v>
-      </c>
-      <c r="B82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" t="s">
-        <v>120</v>
-      </c>
-      <c r="D82" t="s">
-        <v>155</v>
-      </c>
-      <c r="E82" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>19330051920037</v>
-      </c>
-      <c r="B83" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
-      <c r="D83" t="s">
-        <v>156</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>19330051920037</v>
-      </c>
-      <c r="B84" t="s">
-        <v>94</v>
-      </c>
-      <c r="C84" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" t="s">
-        <v>156</v>
-      </c>
-      <c r="E84" t="s">
-        <v>5</v>
-      </c>
-      <c r="F84" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>19330051920037</v>
-      </c>
-      <c r="B85" t="s">
-        <v>94</v>
-      </c>
-      <c r="C85" t="s">
-        <v>121</v>
-      </c>
-      <c r="D85" t="s">
-        <v>156</v>
-      </c>
-      <c r="E85" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>19330051920036</v>
-      </c>
-      <c r="B86" t="s">
-        <v>95</v>
-      </c>
-      <c r="C86" t="s">
-        <v>87</v>
-      </c>
-      <c r="D86" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" t="s">
-        <v>6</v>
-      </c>
-      <c r="F86" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>19330051920036</v>
-      </c>
-      <c r="B87" t="s">
-        <v>95</v>
-      </c>
-      <c r="C87" t="s">
-        <v>87</v>
-      </c>
-      <c r="D87" t="s">
-        <v>157</v>
-      </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>19330051920036</v>
-      </c>
-      <c r="B88" t="s">
-        <v>95</v>
-      </c>
-      <c r="C88" t="s">
-        <v>87</v>
-      </c>
-      <c r="D88" t="s">
-        <v>157</v>
-      </c>
-      <c r="E88" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>19330051920036</v>
-      </c>
-      <c r="B89" t="s">
-        <v>95</v>
-      </c>
-      <c r="C89" t="s">
-        <v>87</v>
-      </c>
-      <c r="D89" t="s">
-        <v>157</v>
-      </c>
-      <c r="E89" t="s">
-        <v>7</v>
-      </c>
-      <c r="F89" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920036</v>
-      </c>
-      <c r="B90" t="s">
-        <v>95</v>
-      </c>
-      <c r="C90" t="s">
-        <v>87</v>
-      </c>
-      <c r="D90" t="s">
-        <v>157</v>
-      </c>
-      <c r="E90" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920039</v>
-      </c>
-      <c r="B91" t="s">
-        <v>96</v>
-      </c>
-      <c r="C91" t="s">
-        <v>122</v>
-      </c>
-      <c r="D91" t="s">
-        <v>158</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920039</v>
-      </c>
-      <c r="B92" t="s">
-        <v>96</v>
-      </c>
-      <c r="C92" t="s">
-        <v>122</v>
-      </c>
-      <c r="D92" t="s">
-        <v>158</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920039</v>
-      </c>
-      <c r="B93" t="s">
-        <v>96</v>
-      </c>
-      <c r="C93" t="s">
-        <v>122</v>
-      </c>
-      <c r="D93" t="s">
-        <v>158</v>
-      </c>
-      <c r="E93" t="s">
-        <v>8</v>
-      </c>
-      <c r="F93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920040</v>
-      </c>
-      <c r="B94" t="s">
-        <v>97</v>
-      </c>
-      <c r="C94" t="s">
-        <v>121</v>
-      </c>
-      <c r="D94" t="s">
-        <v>128</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>19330051920040</v>
-      </c>
-      <c r="B95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C95" t="s">
-        <v>121</v>
-      </c>
-      <c r="D95" t="s">
-        <v>128</v>
-      </c>
-      <c r="E95" t="s">
-        <v>5</v>
-      </c>
-      <c r="F95" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>19330051920040</v>
-      </c>
-      <c r="B96" t="s">
-        <v>97</v>
-      </c>
-      <c r="C96" t="s">
-        <v>121</v>
-      </c>
-      <c r="D96" t="s">
-        <v>128</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
         <v>60</v>
       </c>
     </row>
@@ -6309,16 +6012,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920005</v>
+        <v>19330051920004</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -6326,16 +6029,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920004</v>
+        <v>19330051920008</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -6343,16 +6046,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920006</v>
+        <v>19330051920016</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -6360,16 +6063,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920008</v>
+        <v>19330051920015</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -6377,16 +6080,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920016</v>
+        <v>19330051920017</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -6394,16 +6097,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920015</v>
+        <v>19330051920018</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -6411,16 +6114,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920012</v>
+        <v>18330051920168</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -6428,16 +6131,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920011</v>
+        <v>19330051920023</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -6445,16 +6148,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920009</v>
+        <v>19330051920026</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -6462,16 +6165,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920010</v>
+        <v>19330051920027</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -6479,16 +6182,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920017</v>
+        <v>19330051920038</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -6496,257 +6199,257 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920018</v>
+        <v>19330051920005</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>18330051920168</v>
+        <v>19330051920006</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920020</v>
+        <v>19330051920012</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920022</v>
+        <v>19330051920011</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920021</v>
+        <v>19330051920009</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920023</v>
+        <v>19330051920010</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920026</v>
+        <v>19330051920020</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>18330061460390</v>
+        <v>19330051920022</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920025</v>
+        <v>19330051920021</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920027</v>
+        <v>18330061460390</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920029</v>
+        <v>19330051920025</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920030</v>
+        <v>19330051920029</v>
       </c>
       <c r="B36" t="s">
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920031</v>
+        <v>19330051920030</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920035</v>
+        <v>19330051920031</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>19330051920038</v>
+        <v>19330051920035</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6756,7 +6459,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6834,16 +6537,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920005</v>
+        <v>19330051920004</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6857,16 +6560,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920005</v>
+        <v>19330051920004</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6880,16 +6583,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920004</v>
+        <v>19330051920008</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6903,16 +6606,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920004</v>
+        <v>19330051920008</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -6926,16 +6629,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920006</v>
+        <v>19330051920016</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6949,16 +6652,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920006</v>
+        <v>19330051920016</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -6972,16 +6675,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920008</v>
+        <v>19330051920015</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6995,16 +6698,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920008</v>
+        <v>19330051920015</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -7018,16 +6721,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920016</v>
+        <v>19330051920012</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -7041,39 +6744,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920016</v>
+        <v>19330051920012</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920015</v>
+        <v>19330051920011</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7087,39 +6790,39 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920015</v>
+        <v>19330051920011</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920009</v>
+        <v>19330051920010</v>
       </c>
       <c r="B16" t="s">
         <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7133,25 +6836,25 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920009</v>
+        <v>19330051920010</v>
       </c>
       <c r="B17" t="s">
         <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7294,16 +6997,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920020</v>
+        <v>19330051920023</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -7317,16 +7020,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920020</v>
+        <v>19330051920023</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -7340,16 +7043,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>19330051920022</v>
+        <v>19330051920026</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
         <v>6</v>
@@ -7363,16 +7066,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920022</v>
+        <v>19330051920026</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -7386,16 +7089,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -7409,16 +7112,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -7432,16 +7135,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>19330051920023</v>
+        <v>19330051920038</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -7455,16 +7158,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>19330051920023</v>
+        <v>19330051920038</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -7478,16 +7181,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>19330051920026</v>
+        <v>19330051920005</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -7501,22 +7204,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920026</v>
+        <v>19330051920006</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -7524,16 +7227,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>18330061460390</v>
+        <v>19330051920009</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -7547,22 +7250,22 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>18330061460390</v>
+        <v>19330051920020</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G35">
         <v>-1</v>
@@ -7570,16 +7273,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>19330051920025</v>
+        <v>19330051920022</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
@@ -7593,22 +7296,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>19330051920025</v>
+        <v>19330051920021</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G37">
         <v>-1</v>
@@ -7616,16 +7319,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>19330051920027</v>
+        <v>18330061460390</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E38" t="s">
         <v>6</v>
@@ -7639,22 +7342,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920027</v>
+        <v>19330051920025</v>
       </c>
       <c r="B39" t="s">
         <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G39">
         <v>-1</v>
@@ -7685,22 +7388,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920029</v>
+        <v>19330051920030</v>
       </c>
       <c r="B41" t="s">
         <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G41">
         <v>-1</v>
@@ -7708,16 +7411,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>19330051920030</v>
+        <v>19330051920031</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
@@ -7731,162 +7434,24 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>19330051920030</v>
+        <v>19330051920035</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
         <v>88</v>
       </c>
       <c r="D43" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>19330051920031</v>
-      </c>
-      <c r="B44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>19330051920031</v>
-      </c>
-      <c r="B45" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" t="s">
-        <v>119</v>
-      </c>
-      <c r="D45" t="s">
-        <v>152</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>19330051920035</v>
-      </c>
-      <c r="B46" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>59</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>19330051920035</v>
-      </c>
-      <c r="B47" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" t="s">
-        <v>88</v>
-      </c>
-      <c r="D47" t="s">
-        <v>153</v>
-      </c>
-      <c r="E47" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>19330051920038</v>
-      </c>
-      <c r="B48" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" t="s">
-        <v>155</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>19330051920038</v>
-      </c>
-      <c r="B49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" t="s">
-        <v>155</v>
-      </c>
-      <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" t="s">
-        <v>60</v>
-      </c>
-      <c r="G49">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -200,12 +200,12 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
@@ -227,6 +227,153 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>ESTEFANY SARAI</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -239,81 +386,30 @@
     <t>BALDEZ</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>ENCARNACION</t>
   </si>
   <si>
     <t>ELIZALDE</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
     <t>SEGURA</t>
   </si>
   <si>
     <t>TZANAHUA</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VALDERRAMA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
     <t>MORAN</t>
   </si>
   <si>
@@ -326,69 +422,27 @@
     <t>IXTACUA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>PALAGOT</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>BELTRAN</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>YEPEZ</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MELLADO</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
@@ -398,48 +452,21 @@
     <t>ALEX SAUL</t>
   </si>
   <si>
-    <t>FERNANDO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTIAN ANTONIO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>JESSICA</t>
   </si>
   <si>
     <t>ALBERTO</t>
   </si>
   <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
     <t>HAZIEL</t>
   </si>
   <si>
     <t>GIOVANNA</t>
   </si>
   <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
     <t>YAIR ANTONIO</t>
   </si>
   <si>
-    <t>ESTEFANY SARAI</t>
-  </si>
-  <si>
     <t>HUGO</t>
   </si>
   <si>
@@ -449,52 +476,25 @@
     <t>JAIR</t>
   </si>
   <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
     <t>DIANA AMEYALLI</t>
   </si>
   <si>
     <t>ANUAR ANTONIO</t>
   </si>
   <si>
-    <t>ELIDETH</t>
-  </si>
-  <si>
     <t>GAEL</t>
   </si>
   <si>
     <t>ARLETH</t>
   </si>
   <si>
-    <t>YAMIL ELIEL</t>
-  </si>
-  <si>
     <t>JAHIR</t>
   </si>
   <si>
     <t>JOCELYN BERENICE</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>ALAN EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -995,7 +995,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>-1</v>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -1049,7 +1049,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1060,7 +1060,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -1072,7 +1072,7 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>-1</v>
@@ -1114,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>10</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1137,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1214,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -1268,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1445,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1511,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1599,7 +1599,7 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1676,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1730,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>5</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>-1</v>
@@ -1896,7 +1896,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1907,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -1919,7 +1919,7 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -1961,7 +1961,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1973,7 +1973,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -1996,7 +1996,7 @@
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H17">
         <v>-1</v>
@@ -2038,7 +2038,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -2050,7 +2050,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2061,7 +2061,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>9</v>
@@ -2115,7 +2115,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2138,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>10</v>
@@ -2192,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -2227,7 +2227,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2269,7 +2269,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2281,7 +2281,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2369,7 +2369,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>10</v>
@@ -2423,7 +2423,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>10</v>
@@ -2500,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2523,7 +2523,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D24">
         <v>10</v>
@@ -2577,7 +2577,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>10</v>
@@ -2831,7 +2831,7 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -2843,7 +2843,7 @@
         <v>8</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H28">
         <v>-1</v>
@@ -2885,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
         <v>6</v>
@@ -2897,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2908,7 +2908,7 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D29">
         <v>10</v>
@@ -2962,7 +2962,7 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>10</v>
@@ -2985,7 +2985,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>10</v>
@@ -2997,7 +2997,7 @@
         <v>9</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -3039,7 +3039,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>10</v>
@@ -3051,7 +3051,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3062,7 +3062,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>8</v>
@@ -3116,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>8</v>
@@ -3139,7 +3139,7 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D32">
         <v>10</v>
@@ -3193,7 +3193,7 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3216,7 +3216,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -3270,7 +3270,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3305,7 +3305,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
         <v>-1</v>
@@ -3359,7 +3359,7 @@
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3382,7 +3382,7 @@
         <v>5</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3436,7 +3436,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3447,7 +3447,7 @@
         <v>10</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>10</v>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>10</v>
@@ -3536,7 +3536,7 @@
         <v>5</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3590,7 +3590,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3601,7 +3601,7 @@
         <v>-1</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -3613,7 +3613,7 @@
         <v>6</v>
       </c>
       <c r="G38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3655,7 +3655,7 @@
         <v>-1</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>6</v>
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3690,7 +3690,7 @@
         <v>9</v>
       </c>
       <c r="G39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H39">
         <v>-1</v>
@@ -3744,7 +3744,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3755,7 +3755,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D40">
         <v>6</v>
@@ -3767,7 +3767,7 @@
         <v>5</v>
       </c>
       <c r="G40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H40">
         <v>-1</v>
@@ -3809,7 +3809,7 @@
         <v>6</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V40">
         <v>6</v>
@@ -3821,7 +3821,7 @@
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3832,7 +3832,7 @@
         <v>-1</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -3886,7 +3886,7 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -3963,27 +3963,30 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>9.1</v>
+      </c>
       <c r="I2">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -3992,30 +3995,30 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E3">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>68.42</v>
+      </c>
+      <c r="G3">
+        <v>31.58</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>39.47</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8.6</v>
-      </c>
-      <c r="I3">
-        <v>23</v>
-      </c>
-      <c r="J3">
-        <v>60.53</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4024,25 +4027,25 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="G4">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4148,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4177,16 +4180,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920003</v>
+        <v>19330051920417</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4197,96 +4200,96 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920003</v>
+        <v>19330051920417</v>
       </c>
       <c r="B3" t="s">
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920005</v>
+        <v>19330051920417</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920004</v>
+        <v>19330051920417</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
         <v>100</v>
       </c>
-      <c r="D5" t="s">
-        <v>125</v>
-      </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920004</v>
+        <v>19330051920417</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
         <v>100</v>
       </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920006</v>
+        <v>19330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
         <v>101</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -4297,116 +4300,116 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920417</v>
+        <v>19330051920014</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
         <v>102</v>
       </c>
-      <c r="D11" t="s">
-        <v>126</v>
-      </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920417</v>
+        <v>19330051920014</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" t="s">
         <v>102</v>
       </c>
-      <c r="D12" t="s">
-        <v>126</v>
-      </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920007</v>
+        <v>19330051920012</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
         <v>103</v>
-      </c>
-      <c r="D13" t="s">
-        <v>127</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -4417,76 +4420,76 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920007</v>
+        <v>19330051920010</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920007</v>
+        <v>19330051920017</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920007</v>
+        <v>19330051920018</v>
       </c>
       <c r="B16" t="s">
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920008</v>
+        <v>19330051920422</v>
       </c>
       <c r="B17" t="s">
         <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -4497,136 +4500,136 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920008</v>
+        <v>19330051920422</v>
       </c>
       <c r="B18" t="s">
         <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920014</v>
+        <v>19330051920422</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920014</v>
+        <v>19330051920422</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920014</v>
+        <v>19330051920023</v>
       </c>
       <c r="B21" t="s">
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920016</v>
+        <v>19330051920023</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920016</v>
+        <v>18330061460390</v>
       </c>
       <c r="B23" t="s">
         <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920015</v>
+        <v>19330051920024</v>
       </c>
       <c r="B24" t="s">
         <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
@@ -4637,76 +4640,76 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920015</v>
+        <v>19330051920024</v>
       </c>
       <c r="B25" t="s">
         <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920012</v>
+        <v>19330051920024</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920011</v>
+        <v>19330051920024</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920009</v>
+        <v>19330051920032</v>
       </c>
       <c r="B28" t="s">
         <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -4717,216 +4720,216 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920010</v>
+        <v>19330051920032</v>
       </c>
       <c r="B29" t="s">
         <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920017</v>
+        <v>19330051920032</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" t="s">
         <v>111</v>
       </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920017</v>
+        <v>19330051920034</v>
       </c>
       <c r="B31" t="s">
         <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920018</v>
+        <v>19330051920034</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" t="s">
         <v>112</v>
       </c>
-      <c r="D32" t="s">
-        <v>137</v>
-      </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920018</v>
+        <v>19330051920038</v>
       </c>
       <c r="B33" t="s">
         <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>18330051920168</v>
+        <v>19330051920037</v>
       </c>
       <c r="B34" t="s">
         <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>18330051920168</v>
+        <v>19330051920036</v>
       </c>
       <c r="B35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920422</v>
+        <v>19330051920036</v>
       </c>
       <c r="B36" t="s">
         <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D36" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920422</v>
+        <v>19330051920036</v>
       </c>
       <c r="B37" t="s">
         <v>83</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D37" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920422</v>
+        <v>19330051920036</v>
       </c>
       <c r="B38" t="s">
         <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>19330051920422</v>
+        <v>19330051920039</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -4937,842 +4940,42 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>19330051920020</v>
+        <v>19330051920040</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>19330051920022</v>
+        <v>19330051920040</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920021</v>
-      </c>
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920023</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>115</v>
-      </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920023</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920026</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" t="s">
-        <v>144</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920026</v>
-      </c>
-      <c r="B46" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>18330061460390</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" t="s">
-        <v>145</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920025</v>
-      </c>
-      <c r="B48" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" t="s">
-        <v>146</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920027</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
-      </c>
-      <c r="C49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920027</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920024</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" t="s">
-        <v>148</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920024</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>117</v>
-      </c>
-      <c r="D52" t="s">
-        <v>148</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920024</v>
-      </c>
-      <c r="B53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C53" t="s">
-        <v>117</v>
-      </c>
-      <c r="D53" t="s">
-        <v>148</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920024</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" t="s">
-        <v>148</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920029</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>83</v>
-      </c>
-      <c r="D55" t="s">
-        <v>149</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920030</v>
-      </c>
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>88</v>
-      </c>
-      <c r="D56" t="s">
-        <v>150</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920032</v>
-      </c>
-      <c r="B57" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" t="s">
-        <v>151</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920032</v>
-      </c>
-      <c r="B58" t="s">
-        <v>89</v>
-      </c>
-      <c r="C58" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920032</v>
-      </c>
-      <c r="B59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C59" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" t="s">
-        <v>151</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920032</v>
-      </c>
-      <c r="B60" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" t="s">
-        <v>118</v>
-      </c>
-      <c r="D60" t="s">
-        <v>151</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920031</v>
-      </c>
-      <c r="B61" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" t="s">
-        <v>152</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920035</v>
-      </c>
-      <c r="B62" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" t="s">
-        <v>153</v>
-      </c>
-      <c r="E62" t="s">
-        <v>6</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920034</v>
-      </c>
-      <c r="B63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" t="s">
-        <v>117</v>
-      </c>
-      <c r="D63" t="s">
-        <v>154</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920034</v>
-      </c>
-      <c r="B64" t="s">
-        <v>92</v>
-      </c>
-      <c r="C64" t="s">
-        <v>117</v>
-      </c>
-      <c r="D64" t="s">
-        <v>154</v>
-      </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920034</v>
-      </c>
-      <c r="B65" t="s">
-        <v>92</v>
-      </c>
-      <c r="C65" t="s">
-        <v>117</v>
-      </c>
-      <c r="D65" t="s">
-        <v>154</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920038</v>
-      </c>
-      <c r="B66" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" t="s">
-        <v>120</v>
-      </c>
-      <c r="D66" t="s">
-        <v>155</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920038</v>
-      </c>
-      <c r="B67" t="s">
-        <v>93</v>
-      </c>
-      <c r="C67" t="s">
-        <v>120</v>
-      </c>
-      <c r="D67" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920037</v>
-      </c>
-      <c r="B68" t="s">
-        <v>94</v>
-      </c>
-      <c r="C68" t="s">
-        <v>121</v>
-      </c>
-      <c r="D68" t="s">
-        <v>156</v>
-      </c>
-      <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920037</v>
-      </c>
-      <c r="B69" t="s">
-        <v>94</v>
-      </c>
-      <c r="C69" t="s">
-        <v>121</v>
-      </c>
-      <c r="D69" t="s">
-        <v>156</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920037</v>
-      </c>
-      <c r="B70" t="s">
-        <v>94</v>
-      </c>
-      <c r="C70" t="s">
-        <v>121</v>
-      </c>
-      <c r="D70" t="s">
-        <v>156</v>
-      </c>
-      <c r="E70" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920036</v>
-      </c>
-      <c r="B71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" t="s">
-        <v>87</v>
-      </c>
-      <c r="D71" t="s">
-        <v>157</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920036</v>
-      </c>
-      <c r="B72" t="s">
-        <v>95</v>
-      </c>
-      <c r="C72" t="s">
-        <v>87</v>
-      </c>
-      <c r="D72" t="s">
-        <v>157</v>
-      </c>
-      <c r="E72" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920036</v>
-      </c>
-      <c r="B73" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" t="s">
-        <v>87</v>
-      </c>
-      <c r="D73" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920036</v>
-      </c>
-      <c r="B74" t="s">
-        <v>95</v>
-      </c>
-      <c r="C74" t="s">
-        <v>87</v>
-      </c>
-      <c r="D74" t="s">
-        <v>157</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>19330051920036</v>
-      </c>
-      <c r="B75" t="s">
-        <v>95</v>
-      </c>
-      <c r="C75" t="s">
-        <v>87</v>
-      </c>
-      <c r="D75" t="s">
-        <v>157</v>
-      </c>
-      <c r="E75" t="s">
-        <v>8</v>
-      </c>
-      <c r="F75" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>19330051920039</v>
-      </c>
-      <c r="B76" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" t="s">
-        <v>122</v>
-      </c>
-      <c r="D76" t="s">
-        <v>158</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>19330051920039</v>
-      </c>
-      <c r="B77" t="s">
-        <v>96</v>
-      </c>
-      <c r="C77" t="s">
-        <v>122</v>
-      </c>
-      <c r="D77" t="s">
-        <v>158</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>19330051920039</v>
-      </c>
-      <c r="B78" t="s">
-        <v>96</v>
-      </c>
-      <c r="C78" t="s">
-        <v>122</v>
-      </c>
-      <c r="D78" t="s">
-        <v>158</v>
-      </c>
-      <c r="E78" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>19330051920040</v>
-      </c>
-      <c r="B79" t="s">
-        <v>97</v>
-      </c>
-      <c r="C79" t="s">
-        <v>121</v>
-      </c>
-      <c r="D79" t="s">
-        <v>128</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>19330051920040</v>
-      </c>
-      <c r="B80" t="s">
-        <v>97</v>
-      </c>
-      <c r="C80" t="s">
-        <v>121</v>
-      </c>
-      <c r="D80" t="s">
-        <v>128</v>
-      </c>
-      <c r="E80" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>19330051920040</v>
-      </c>
-      <c r="B81" t="s">
-        <v>97</v>
-      </c>
-      <c r="C81" t="s">
-        <v>121</v>
-      </c>
-      <c r="D81" t="s">
-        <v>128</v>
-      </c>
-      <c r="E81" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5811,13 +5014,13 @@
         <v>19330051920417</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -5825,33 +5028,33 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920036</v>
+        <v>19330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
         <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920007</v>
+        <v>19330051920422</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5859,16 +5062,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920422</v>
+        <v>19330051920024</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -5876,16 +5079,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920024</v>
+        <v>19330051920036</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -5896,16 +5099,16 @@
         <v>19330051920032</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5913,475 +5116,475 @@
         <v>19330051920014</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920034</v>
+        <v>19330051920023</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920037</v>
+        <v>19330051920034</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920039</v>
+        <v>19330051920040</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920040</v>
+        <v>19330051920012</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920003</v>
+        <v>19330051920010</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920004</v>
+        <v>19330051920017</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920008</v>
+        <v>19330051920018</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920016</v>
+        <v>18330061460390</v>
       </c>
       <c r="B16" t="s">
         <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920015</v>
+        <v>19330051920038</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920017</v>
+        <v>19330051920037</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920018</v>
+        <v>19330051920039</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>18330051920168</v>
+        <v>19330051920003</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920023</v>
+        <v>19330051920005</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920026</v>
+        <v>19330051920004</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920027</v>
+        <v>19330051920006</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920038</v>
+        <v>19330051920008</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920005</v>
+        <v>19330051920016</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920006</v>
+        <v>19330051920015</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920012</v>
+        <v>19330051920011</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920011</v>
+        <v>19330051920009</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920009</v>
+        <v>18330051920168</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>125</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920010</v>
+        <v>19330051920020</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920020</v>
+        <v>19330051920022</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920022</v>
+        <v>19330051920021</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920021</v>
+        <v>19330051920026</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>18330061460390</v>
+        <v>19330051920025</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920025</v>
+        <v>19330051920027</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6389,16 +5592,16 @@
         <v>19330051920029</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D36" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6406,16 +5609,16 @@
         <v>19330051920030</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6423,16 +5626,16 @@
         <v>19330051920031</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D38" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6440,16 +5643,16 @@
         <v>19330051920035</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6459,7 +5662,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6491,16 +5694,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920003</v>
+        <v>19330051920012</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6514,39 +5717,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920003</v>
+        <v>19330051920012</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>60</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920004</v>
+        <v>19330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6560,39 +5763,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920004</v>
+        <v>19330051920010</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>60</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920008</v>
+        <v>19330051920023</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6606,22 +5809,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920008</v>
+        <v>19330051920023</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6629,22 +5832,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920016</v>
+        <v>19330051920039</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6652,45 +5855,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920016</v>
+        <v>19330051920039</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920015</v>
+        <v>19330051920040</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -6698,22 +5901,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920015</v>
+        <v>19330051920040</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -6721,68 +5924,68 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920012</v>
+        <v>19330051920011</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920012</v>
+        <v>19330051920017</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>61</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920011</v>
+        <v>19330051920018</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6790,39 +5993,39 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920011</v>
+        <v>18330061460390</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920010</v>
+        <v>19330051920038</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -6836,622 +6039,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920010</v>
+        <v>19330051920037</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920017</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920017</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920018</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>137</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920018</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>18330051920168</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>18330051920168</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920023</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920023</v>
-      </c>
-      <c r="B25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920026</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>19330051920026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>19330051920027</v>
-      </c>
-      <c r="B28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>19330051920027</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>99</v>
-      </c>
-      <c r="D29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920038</v>
-      </c>
-      <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920038</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>19330051920005</v>
-      </c>
-      <c r="B32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>19330051920006</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
-        <v>101</v>
-      </c>
-      <c r="D33" t="s">
-        <v>71</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>19330051920009</v>
-      </c>
-      <c r="B34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" t="s">
-        <v>109</v>
-      </c>
-      <c r="D34" t="s">
-        <v>134</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>19330051920020</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" t="s">
-        <v>140</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>19330051920022</v>
-      </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>19330051920021</v>
-      </c>
-      <c r="B37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" t="s">
-        <v>142</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>18330061460390</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>19330051920025</v>
-      </c>
-      <c r="B39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>19330051920029</v>
-      </c>
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>59</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>19330051920030</v>
-      </c>
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" t="s">
-        <v>150</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>59</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>19330051920031</v>
-      </c>
-      <c r="B42" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D42" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>59</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>19330051920035</v>
-      </c>
-      <c r="B43" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>59</v>
-      </c>
-      <c r="G43">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -197,18 +197,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -239,58 +239,172 @@
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>ESTEFANY SARAI</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDEZ</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
   </si>
   <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>VALDERRAMA</t>
-  </si>
-  <si>
     <t>VEGA</t>
   </si>
   <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>IXTACUA</t>
+  </si>
+  <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>MELENDEZ</t>
@@ -299,19 +413,13 @@
     <t>ARELLANO</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>CHICO</t>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
+  </si>
+  <si>
+    <t>MELLADO</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -320,19 +428,28 @@
     <t>MENCIAS</t>
   </si>
   <si>
-    <t>FERNANDO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTIAN ANTONIO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
   </si>
   <si>
     <t>SAUL ALEJANDRO</t>
@@ -341,160 +458,43 @@
     <t>LOGAN ZURIEL</t>
   </si>
   <si>
-    <t>ESTEFANY SARAI</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>ELIDETH</t>
-  </si>
-  <si>
-    <t>YAMIL ELIEL</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>HUGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>DIANA AMEYALLI</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ARLETH</t>
+  </si>
+  <si>
+    <t>JAHIR</t>
+  </si>
+  <si>
+    <t>JOCELYN BERENICE</t>
   </si>
   <si>
     <t>MAURICIO</t>
   </si>
   <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
     <t>ALAN EDUARDO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
   </si>
 </sst>
 </file>
@@ -998,22 +998,22 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1043,13 +1043,13 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1075,22 +1075,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1152,22 +1152,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1229,22 +1229,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1280,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1288,7 +1288,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1297,16 +1297,16 @@
         <v>-1</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1315,13 +1315,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1342,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1351,13 +1351,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1365,7 +1365,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1380,10 +1380,10 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1392,13 +1392,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1419,7 +1419,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1460,22 +1460,22 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1496,7 +1496,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1511,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1537,22 +1537,22 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1614,22 +1614,22 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1691,22 +1691,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1727,7 +1727,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1768,22 +1768,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1810,10 +1810,10 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1845,7 +1845,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1854,13 +1854,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1881,7 +1881,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1896,7 +1896,7 @@
         <v>5</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1922,22 +1922,22 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1973,7 +1973,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1999,22 +1999,22 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2035,7 +2035,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -2050,7 +2050,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2073,25 +2073,25 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2150,25 +2150,25 @@
         <v>10</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2204,7 +2204,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2230,22 +2230,22 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2281,7 +2281,7 @@
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2298,16 +2298,16 @@
         <v>-1</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F21">
         <v>5</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2316,13 +2316,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2343,7 +2343,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2352,13 +2352,13 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2384,22 +2384,22 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2426,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2461,22 +2461,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2538,22 +2538,22 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2612,25 +2612,25 @@
         <v>8</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2651,22 +2651,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2683,16 +2683,16 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
         <v>5</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2701,13 +2701,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2728,7 +2728,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2737,13 +2737,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2769,22 +2769,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2805,13 +2805,13 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2846,22 +2846,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2882,7 +2882,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>9</v>
@@ -2891,13 +2891,13 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2923,22 +2923,22 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2959,7 +2959,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>10</v>
@@ -3000,22 +3000,22 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3036,7 +3036,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3051,7 +3051,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3077,22 +3077,22 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3113,7 +3113,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3154,22 +3154,22 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3190,7 +3190,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -3205,7 +3205,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3231,22 +3231,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3267,7 +3267,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3290,7 +3290,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C34">
         <v>-1</v>
@@ -3299,7 +3299,7 @@
         <v>6</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>5</v>
@@ -3308,7 +3308,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3317,13 +3317,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3344,7 +3344,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3353,13 +3353,13 @@
         <v>6</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3367,7 +3367,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>-1</v>
@@ -3385,7 +3385,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3394,13 +3394,13 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3421,7 +3421,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3436,7 +3436,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3462,22 +3462,22 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3521,7 +3521,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>-1</v>
@@ -3530,7 +3530,7 @@
         <v>-1</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F37">
         <v>5</v>
@@ -3539,7 +3539,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3548,13 +3548,13 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3575,7 +3575,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3584,13 +3584,13 @@
         <v>-1</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3598,7 +3598,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C38">
         <v>8</v>
@@ -3616,22 +3616,22 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I38">
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3652,13 +3652,13 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U38">
         <v>8</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3693,22 +3693,22 @@
         <v>6</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I39">
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3735,7 +3735,7 @@
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>10</v>
@@ -3744,7 +3744,7 @@
         <v>9</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3761,7 +3761,7 @@
         <v>6</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F40">
         <v>5</v>
@@ -3770,7 +3770,7 @@
         <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3779,13 +3779,13 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3806,7 +3806,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3815,13 +3815,13 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X40">
         <v>5</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3829,7 +3829,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -3844,10 +3844,10 @@
         <v>6</v>
       </c>
       <c r="G41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -3856,13 +3856,13 @@
         <v>-1</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3883,7 +3883,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U41">
         <v>7</v>
@@ -3892,13 +3892,13 @@
         <v>8</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>6</v>
       </c>
       <c r="Y41">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -3963,30 +3963,30 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E2">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>52.63</v>
+      </c>
+      <c r="G2">
+        <v>47.37</v>
+      </c>
+      <c r="H2">
+        <v>6.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>9.1</v>
-      </c>
-      <c r="I2">
-        <v>13</v>
-      </c>
-      <c r="J2">
-        <v>34.21</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -3995,30 +3995,30 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>68.42</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="G3">
-        <v>31.58</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4027,30 +4027,30 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E4">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="G4">
+        <v>34.21</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>78.95</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>21.05</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4059,25 +4059,25 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>68.42</v>
+      </c>
+      <c r="G5">
+        <v>31.58</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>81.58</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.3</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>18.42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4103,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -4123,25 +4123,25 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4151,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4186,16 +4186,16 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4206,50 +4206,50 @@
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4260,722 +4260,302 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920417</v>
+        <v>19330051920014</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920007</v>
+        <v>19330051920014</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920007</v>
+        <v>19330051920012</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920007</v>
+        <v>19330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920007</v>
+        <v>19330051920422</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920014</v>
+        <v>19330051920422</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920014</v>
+        <v>19330051920023</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920012</v>
+        <v>18330061460390</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920010</v>
+        <v>19330051920024</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920017</v>
+        <v>19330051920024</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920018</v>
+        <v>19330051920032</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920422</v>
+        <v>19330051920034</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920422</v>
+        <v>19330051920038</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920422</v>
+        <v>19330051920036</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920422</v>
+        <v>19330051920036</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920023</v>
-      </c>
-      <c r="B21" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920023</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>18330061460390</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920024</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920024</v>
-      </c>
-      <c r="B25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920024</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920024</v>
-      </c>
-      <c r="B27" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920032</v>
-      </c>
-      <c r="B28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920032</v>
-      </c>
-      <c r="B29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920032</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920034</v>
-      </c>
-      <c r="B31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920034</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920038</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920037</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920036</v>
-      </c>
-      <c r="B35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920036</v>
-      </c>
-      <c r="B36" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s">
-        <v>115</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920036</v>
-      </c>
-      <c r="B37" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920036</v>
-      </c>
-      <c r="B38" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" t="s">
-        <v>115</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920039</v>
-      </c>
-      <c r="B39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" t="s">
-        <v>116</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920040</v>
-      </c>
-      <c r="B40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>117</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920040</v>
-      </c>
-      <c r="B41" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>117</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -5017,13 +4597,13 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5034,163 +4614,163 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920422</v>
+        <v>19330051920014</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920024</v>
+        <v>19330051920422</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920036</v>
+        <v>19330051920024</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920032</v>
+        <v>19330051920036</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920014</v>
+        <v>19330051920012</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920023</v>
+        <v>19330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920034</v>
+        <v>19330051920023</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920040</v>
+        <v>18330061460390</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920012</v>
+        <v>19330051920032</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5198,16 +4778,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920010</v>
+        <v>19330051920034</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5215,16 +4795,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920017</v>
+        <v>19330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
         <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5232,101 +4812,101 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920018</v>
+        <v>19330051920003</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>18330061460390</v>
+        <v>19330051920005</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920038</v>
+        <v>19330051920004</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920037</v>
+        <v>19330051920006</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920039</v>
+        <v>19330051920008</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920003</v>
+        <v>19330051920016</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5334,16 +4914,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920005</v>
+        <v>19330051920015</v>
       </c>
       <c r="B21" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5351,16 +4931,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920004</v>
+        <v>19330051920011</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5368,16 +4948,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920006</v>
+        <v>19330051920009</v>
       </c>
       <c r="B23" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5385,16 +4965,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920008</v>
+        <v>19330051920017</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5402,16 +4982,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920016</v>
+        <v>19330051920018</v>
       </c>
       <c r="B25" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5419,16 +4999,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920015</v>
+        <v>18330051920168</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5436,16 +5016,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920011</v>
+        <v>19330051920020</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5453,16 +5033,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920009</v>
+        <v>19330051920022</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5470,16 +5050,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>18330051920168</v>
+        <v>19330051920021</v>
       </c>
       <c r="B29" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5487,16 +5067,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920020</v>
+        <v>19330051920026</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5504,16 +5084,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920022</v>
+        <v>19330051920025</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5521,16 +5101,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5538,16 +5118,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920026</v>
+        <v>19330051920029</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5555,16 +5135,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920025</v>
+        <v>19330051920030</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5572,16 +5152,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920027</v>
+        <v>19330051920031</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5589,16 +5169,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920029</v>
+        <v>19330051920035</v>
       </c>
       <c r="B36" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5606,16 +5186,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920030</v>
+        <v>19330051920037</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5623,16 +5203,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>19330051920031</v>
+        <v>19330051920039</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5640,16 +5220,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>19330051920035</v>
+        <v>19330051920040</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5662,7 +5242,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5700,16 +5280,16 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5723,16 +5303,16 @@
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5746,16 +5326,16 @@
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5769,16 +5349,16 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5786,91 +5366,91 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920023</v>
+        <v>18330051920168</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920023</v>
+        <v>18330051920168</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920039</v>
+        <v>19330051920026</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920039</v>
+        <v>19330051920026</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5878,45 +5458,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920040</v>
+        <v>18330061460390</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920040</v>
+        <v>18330061460390</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5924,140 +5504,278 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920011</v>
+        <v>19330051920038</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920017</v>
+        <v>19330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920018</v>
+        <v>19330051920037</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>61</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>18330061460390</v>
+        <v>19330051920037</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
         <v>59</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920038</v>
+        <v>19330051920003</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
         <v>59</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920037</v>
+        <v>19330051920004</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920016</v>
+      </c>
+      <c r="B18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920011</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920017</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920018</v>
+      </c>
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920023</v>
+      </c>
+      <c r="B22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" t="s">
         <v>98</v>
       </c>
-      <c r="D17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920040</v>
+      </c>
+      <c r="B23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -200,15 +200,15 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -236,49 +236,154 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ESTEFANY SARAI</t>
+  </si>
+  <si>
+    <t>ELIDETH</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDEZ</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>RIOS</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>ROMAN</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>SERRANO</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VALDERRAMA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>IXTACUA</t>
+  </si>
+  <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>SORIANO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
   </si>
   <si>
     <t>CHAVEZ</t>
@@ -287,208 +392,103 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>MELLADO</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>FERNANDO DE JESUS</t>
-  </si>
-  <si>
-    <t>CRISTIAN ANTONIO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
   </si>
   <si>
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
+  </si>
+  <si>
     <t>JESUS</t>
   </si>
   <si>
-    <t>ESTEFANY SARAI</t>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>HUGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>JAIR</t>
   </si>
   <si>
     <t>JOSE AUGUSTO</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>NATANAEL</t>
   </si>
   <si>
-    <t>ELIDETH</t>
+    <t>DIANA AMEYALLI</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ARLETH</t>
   </si>
   <si>
     <t>YAMIL ELIEL</t>
   </si>
   <si>
+    <t>JAHIR</t>
+  </si>
+  <si>
+    <t>JOCELYN BERENICE</t>
+  </si>
+  <si>
     <t>JOHNNY</t>
   </si>
   <si>
     <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
   </si>
   <si>
     <t>MAURICIO</t>
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -1078,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1087,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1155,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1200,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -1241,7 +1241,7 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1268,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1291,7 +1291,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>-1</v>
@@ -1309,7 +1309,7 @@
         <v>5</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1318,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1368,7 +1368,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>-1</v>
@@ -1395,7 +1395,7 @@
         <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1422,7 +1422,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1522,7 +1522,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>8</v>
@@ -1540,7 +1540,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>8</v>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -1576,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -1626,7 +1626,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1653,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>10</v>
@@ -1703,7 +1703,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1771,7 +1771,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -1780,7 +1780,7 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1830,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1884,7 +1884,7 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -1925,7 +1925,7 @@
         <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>10</v>
@@ -1934,7 +1934,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>8</v>
@@ -2002,7 +2002,7 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -2011,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -2047,7 +2047,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -2079,7 +2079,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>9</v>
@@ -2088,7 +2088,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>5</v>
@@ -2115,7 +2115,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
@@ -2156,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>10</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2233,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>6</v>
@@ -2242,7 +2242,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2269,7 +2269,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2292,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>-1</v>
@@ -2319,7 +2319,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2346,7 +2346,7 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2387,7 +2387,7 @@
         <v>8</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>7</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2432,7 +2432,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -2473,7 +2473,7 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2500,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2509,7 +2509,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2541,7 +2541,7 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>6</v>
@@ -2600,7 +2600,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2618,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>8</v>
@@ -2627,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2654,7 +2654,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2663,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2677,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2704,7 +2704,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>5</v>
@@ -2731,7 +2731,7 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -2754,7 +2754,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -2772,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>8</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -2808,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2817,7 +2817,7 @@
         <v>10</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2849,7 +2849,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -2858,7 +2858,7 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -2926,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
         <v>10</v>
@@ -2935,7 +2935,7 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -3003,7 +3003,7 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>10</v>
@@ -3012,7 +3012,7 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -3048,7 +3048,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3080,7 +3080,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -3089,7 +3089,7 @@
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -3157,7 +3157,7 @@
         <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -3166,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -3234,7 +3234,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -3243,7 +3243,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3293,7 +3293,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>6</v>
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3320,7 +3320,7 @@
         <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>5</v>
@@ -3347,7 +3347,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>6</v>
@@ -3370,7 +3370,7 @@
         <v>5</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -3388,7 +3388,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3397,7 +3397,7 @@
         <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>5</v>
@@ -3424,7 +3424,7 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V35">
         <v>6</v>
@@ -3433,7 +3433,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3465,7 +3465,7 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>10</v>
@@ -3474,7 +3474,7 @@
         <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>6</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>-1</v>
@@ -3542,7 +3542,7 @@
         <v>5</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3551,7 +3551,7 @@
         <v>7</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>5</v>
@@ -3578,7 +3578,7 @@
         <v>5</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>-1</v>
@@ -3619,7 +3619,7 @@
         <v>5</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>7</v>
@@ -3628,7 +3628,7 @@
         <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>5</v>
@@ -3655,7 +3655,7 @@
         <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>7</v>
@@ -3678,7 +3678,7 @@
         <v>6</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>10</v>
@@ -3696,7 +3696,7 @@
         <v>6</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
         <v>8</v>
@@ -3705,7 +3705,7 @@
         <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>5</v>
@@ -3732,7 +3732,7 @@
         <v>6</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -3741,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3773,7 +3773,7 @@
         <v>5</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -3782,7 +3782,7 @@
         <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3859,7 +3859,7 @@
         <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>5</v>
@@ -3895,7 +3895,7 @@
         <v>9</v>
       </c>
       <c r="X41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y41">
         <v>6</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -3998,27 +3998,27 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>65.79000000000001</v>
       </c>
       <c r="G3">
+        <v>34.21</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>9.1</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
       <c r="J3">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4027,19 +4027,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>65.79000000000001</v>
+        <v>71.05</v>
       </c>
       <c r="G4">
-        <v>34.21</v>
+        <v>28.95</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4059,19 +4059,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="G5">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4151,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4186,30 +4186,30 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920417</v>
+        <v>19330051920007</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
         <v>81</v>
-      </c>
-      <c r="D3" t="s">
-        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4220,36 +4220,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920007</v>
+        <v>19330051920014</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" t="s">
         <v>82</v>
       </c>
-      <c r="D4" t="s">
-        <v>93</v>
-      </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920007</v>
+        <v>19330051920422</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -4260,301 +4260,41 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920014</v>
+        <v>19330051920024</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920014</v>
+        <v>19330051920036</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920012</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920422</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920422</v>
-      </c>
-      <c r="B11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920023</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>18330061460390</v>
-      </c>
-      <c r="B13" t="s">
-        <v>75</v>
-      </c>
-      <c r="C13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920024</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920024</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920032</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920034</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>102</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920038</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920036</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920036</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4597,13 +4337,13 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4614,13 +4354,13 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4631,13 +4371,13 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4645,16 +4385,16 @@
         <v>19330051920422</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4662,16 +4402,16 @@
         <v>19330051920024</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4679,149 +4419,149 @@
         <v>19330051920036</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920012</v>
+        <v>19330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920010</v>
+        <v>19330051920005</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920023</v>
+        <v>19330051920004</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>18330061460390</v>
+        <v>19330051920006</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
         <v>88</v>
       </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920032</v>
+        <v>19330051920008</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920034</v>
+        <v>19330051920016</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920038</v>
+        <v>19330051920015</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920003</v>
+        <v>19330051920012</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4829,16 +4569,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920005</v>
+        <v>19330051920011</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4846,16 +4586,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920004</v>
+        <v>19330051920009</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4863,16 +4603,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920006</v>
+        <v>19330051920010</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4880,13 +4620,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920008</v>
+        <v>19330051920017</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -4897,13 +4637,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920016</v>
+        <v>19330051920018</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>140</v>
@@ -4914,13 +4654,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920015</v>
+        <v>18330051920168</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
@@ -4931,13 +4671,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920011</v>
+        <v>19330051920020</v>
       </c>
       <c r="B22" t="s">
         <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>142</v>
@@ -4948,13 +4688,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920009</v>
+        <v>19330051920022</v>
       </c>
       <c r="B23" t="s">
         <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>143</v>
@@ -4965,13 +4705,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920017</v>
+        <v>19330051920021</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
         <v>144</v>
@@ -4982,13 +4722,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920018</v>
+        <v>19330051920023</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -4999,13 +4739,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>18330051920168</v>
+        <v>19330051920026</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -5016,13 +4756,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920020</v>
+        <v>18330061460390</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -5033,13 +4773,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920022</v>
+        <v>19330051920025</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -5050,13 +4790,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920021</v>
+        <v>19330051920027</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
         <v>149</v>
@@ -5067,13 +4807,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920026</v>
+        <v>19330051920029</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
         <v>150</v>
@@ -5084,13 +4824,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920025</v>
+        <v>19330051920030</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -5101,13 +4841,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920027</v>
+        <v>19330051920032</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -5118,13 +4858,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920029</v>
+        <v>19330051920031</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -5135,13 +4875,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920030</v>
+        <v>19330051920035</v>
       </c>
       <c r="B34" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -5152,13 +4892,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920031</v>
+        <v>19330051920034</v>
       </c>
       <c r="B35" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -5169,13 +4909,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920035</v>
+        <v>19330051920038</v>
       </c>
       <c r="B36" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
         <v>156</v>
@@ -5189,10 +4929,10 @@
         <v>19330051920037</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -5206,10 +4946,10 @@
         <v>19330051920039</v>
       </c>
       <c r="B38" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
         <v>158</v>
@@ -5223,13 +4963,13 @@
         <v>19330051920040</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5242,7 +4982,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5274,45 +5014,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920012</v>
+        <v>19330051920010</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920012</v>
+        <v>19330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5320,45 +5060,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920010</v>
+        <v>18330051920168</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920010</v>
+        <v>18330051920168</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5366,13 +5106,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920168</v>
+        <v>19330051920026</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D6" t="s">
         <v>146</v>
@@ -5381,7 +5121,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5389,13 +5129,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920168</v>
+        <v>19330051920026</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
         <v>146</v>
@@ -5412,22 +5152,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920026</v>
+        <v>19330051920037</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5435,16 +5175,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920026</v>
+        <v>19330051920037</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5458,22 +5198,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330061460390</v>
+        <v>19330051920040</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5481,62 +5221,62 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330061460390</v>
+        <v>19330051920040</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920038</v>
+        <v>19330051920003</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920038</v>
+        <v>19330051920004</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5550,22 +5290,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920037</v>
+        <v>19330051920016</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5573,22 +5313,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920037</v>
+        <v>19330051920012</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5596,16 +5336,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920003</v>
+        <v>19330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5619,16 +5359,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920004</v>
+        <v>19330051920018</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5642,22 +5382,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920016</v>
+        <v>18330061460390</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -5665,116 +5405,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920011</v>
+        <v>19330051920038</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920017</v>
-      </c>
-      <c r="B20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920018</v>
-      </c>
-      <c r="B21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920023</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920040</v>
-      </c>
-      <c r="B23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -200,18 +200,18 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -227,271 +227,271 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDEZ</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
     <t>CARRASCO</t>
   </si>
   <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
     <t>VALDERRAMA</t>
   </si>
   <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>IXTACUA</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
     <t>SANDOVAL</t>
   </si>
   <si>
+    <t>PALAGOT</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MELLADO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEX SAUL</t>
+  </si>
+  <si>
     <t>FERNANDO DE JESUS</t>
   </si>
   <si>
     <t>CRISTIAN ANTONIO</t>
   </si>
   <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>ALBERTO</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>HAZIEL</t>
+  </si>
+  <si>
+    <t>GIOVANNA</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>SAUL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>LOGAN ZURIEL</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
     <t>ESTEFANY SARAI</t>
   </si>
   <si>
+    <t>HUGO</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JOSE AUGUSTO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>NATANAEL</t>
+  </si>
+  <si>
+    <t>DIANA AMEYALLI</t>
+  </si>
+  <si>
+    <t>ANUAR ANTONIO</t>
+  </si>
+  <si>
     <t>ELIDETH</t>
   </si>
   <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>ARLETH</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>JAHIR</t>
+  </si>
+  <si>
+    <t>JOCELYN BERENICE</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>ERICK ORLANDO</t>
+  </si>
+  <si>
+    <t>MAURICIO</t>
+  </si>
+  <si>
     <t>EMILIO</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>IXTACUA</t>
-  </si>
-  <si>
-    <t>PALAGOT</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BELTRAN</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MELLADO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
-  </si>
-  <si>
-    <t>ALEX SAUL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>ALBERTO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>HAZIEL</t>
-  </si>
-  <si>
-    <t>GIOVANNA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>SAUL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>LOGAN ZURIEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>HUGO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JOSE AUGUSTO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>NATANAEL</t>
-  </si>
-  <si>
-    <t>DIANA AMEYALLI</t>
-  </si>
-  <si>
-    <t>ANUAR ANTONIO</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>ARLETH</t>
-  </si>
-  <si>
-    <t>YAMIL ELIEL</t>
-  </si>
-  <si>
-    <t>JAHIR</t>
-  </si>
-  <si>
-    <t>JOCELYN BERENICE</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>ERICK ORLANDO</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
   </si>
   <si>
     <t>ALAN EDUARDO</t>
@@ -1001,7 +1001,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -1016,19 +1016,19 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1037,7 +1037,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -1093,19 +1093,19 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1170,19 +1170,19 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1200,7 +1200,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1247,19 +1247,19 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1294,7 +1294,7 @@
         <v>5</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>9</v>
@@ -1312,7 +1312,7 @@
         <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>8</v>
@@ -1324,19 +1324,19 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1348,13 +1348,13 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>9</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1371,7 +1371,7 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -1386,10 +1386,10 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1401,19 +1401,19 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1425,13 +1425,13 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1478,19 +1478,19 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1555,25 +1555,25 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1585,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1632,25 +1632,25 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1709,19 +1709,19 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1786,19 +1786,19 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1810,13 +1810,13 @@
         <v>5</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -1848,10 +1848,10 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -1863,37 +1863,37 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>5</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1940,19 +1940,19 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2017,19 +2017,19 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2094,19 +2094,19 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2171,19 +2171,19 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2248,25 +2248,25 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2275,10 +2275,10 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2295,7 +2295,7 @@
         <v>5</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>7</v>
@@ -2310,10 +2310,10 @@
         <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>7</v>
@@ -2325,31 +2325,31 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2402,19 +2402,19 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2426,7 +2426,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2479,19 +2479,19 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2509,7 +2509,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2556,19 +2556,19 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2633,31 +2633,31 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>7</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2680,7 +2680,7 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2698,7 +2698,7 @@
         <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>7</v>
@@ -2710,37 +2710,37 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2787,25 +2787,25 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2864,31 +2864,31 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>9</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2941,19 +2941,19 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3018,19 +3018,19 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3048,7 +3048,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -3095,19 +3095,19 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3172,19 +3172,19 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3249,19 +3249,19 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3314,7 +3314,7 @@
         <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -3326,19 +3326,19 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3350,13 +3350,13 @@
         <v>5</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>5</v>
@@ -3391,7 +3391,7 @@
         <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -3403,25 +3403,25 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>5</v>
@@ -3430,10 +3430,10 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3480,19 +3480,19 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3527,7 +3527,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E37">
         <v>7</v>
@@ -3545,7 +3545,7 @@
         <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>7</v>
@@ -3557,31 +3557,31 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>5</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W37">
         <v>7</v>
@@ -3634,25 +3634,25 @@
         <v>5</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3711,19 +3711,19 @@
         <v>5</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3776,7 +3776,7 @@
         <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>7</v>
@@ -3788,25 +3788,25 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U40">
         <v>6</v>
@@ -3815,10 +3815,10 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3850,10 +3850,10 @@
         <v>5</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
         <v>7</v>
@@ -3865,19 +3865,19 @@
         <v>5</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3886,13 +3886,13 @@
         <v>5</v>
       </c>
       <c r="U41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X41">
         <v>5</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -3995,19 +3995,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="G3">
-        <v>34.21</v>
+        <v>21.05</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4027,19 +4027,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>71.05</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G4">
-        <v>28.95</v>
+        <v>15.79</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4059,19 +4059,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>78.95</v>
+        <v>86.84</v>
       </c>
       <c r="G5">
-        <v>21.05</v>
+        <v>13.16</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -4091,25 +4091,25 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>84.20999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>7.89</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4151,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4176,126 +4176,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920417</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920007</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920014</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920422</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920024</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920036</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -4331,118 +4211,118 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920417</v>
+        <v>19330051920003</v>
       </c>
       <c r="B2" t="s">
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920007</v>
+        <v>19330051920005</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920014</v>
+        <v>19330051920004</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920422</v>
+        <v>19330051920006</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920024</v>
+        <v>19330051920417</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920036</v>
+        <v>19330051920007</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920003</v>
+        <v>19330051920008</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4450,16 +4330,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920005</v>
+        <v>19330051920014</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4467,16 +4347,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920004</v>
+        <v>19330051920016</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4484,16 +4364,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920006</v>
+        <v>19330051920015</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4501,13 +4381,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920008</v>
+        <v>19330051920012</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>132</v>
@@ -4518,13 +4398,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920016</v>
+        <v>19330051920011</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -4535,13 +4415,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920015</v>
+        <v>19330051920009</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -4552,13 +4432,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920012</v>
+        <v>19330051920010</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D15" t="s">
         <v>135</v>
@@ -4569,13 +4449,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920011</v>
+        <v>19330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
         <v>136</v>
@@ -4586,13 +4466,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920009</v>
+        <v>19330051920018</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
         <v>137</v>
@@ -4603,13 +4483,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920010</v>
+        <v>18330051920168</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
         <v>138</v>
@@ -4620,13 +4500,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920017</v>
+        <v>19330051920422</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -4637,13 +4517,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920018</v>
+        <v>19330051920020</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>140</v>
@@ -4654,13 +4534,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>18330051920168</v>
+        <v>19330051920022</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
@@ -4671,13 +4551,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920020</v>
+        <v>19330051920021</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>142</v>
@@ -4688,13 +4568,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920022</v>
+        <v>19330051920023</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>143</v>
@@ -4705,13 +4585,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920021</v>
+        <v>19330051920026</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
         <v>144</v>
@@ -4722,13 +4602,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920023</v>
+        <v>18330061460390</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -4739,13 +4619,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920026</v>
+        <v>19330051920025</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -4756,13 +4636,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>18330061460390</v>
+        <v>19330051920027</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -4773,13 +4653,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920025</v>
+        <v>19330051920024</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -4790,13 +4670,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920027</v>
+        <v>19330051920029</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
         <v>149</v>
@@ -4807,13 +4687,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920029</v>
+        <v>19330051920030</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
         <v>150</v>
@@ -4824,13 +4704,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920030</v>
+        <v>19330051920032</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -4841,13 +4721,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920032</v>
+        <v>19330051920031</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -4858,13 +4738,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920031</v>
+        <v>19330051920035</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -4875,13 +4755,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>19330051920035</v>
+        <v>19330051920034</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -4892,13 +4772,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>19330051920034</v>
+        <v>19330051920038</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -4909,13 +4789,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>19330051920038</v>
+        <v>19330051920037</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
         <v>156</v>
@@ -4926,13 +4806,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>19330051920037</v>
+        <v>19330051920036</v>
       </c>
       <c r="B37" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -4946,10 +4826,10 @@
         <v>19330051920039</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D38" t="s">
         <v>158</v>
@@ -4963,13 +4843,13 @@
         <v>19330051920040</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -4982,7 +4862,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5014,22 +4894,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920010</v>
+        <v>19330051920034</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
         <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5037,22 +4917,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920010</v>
+        <v>19330051920034</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
         <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5060,22 +4940,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>18330051920168</v>
+        <v>19330051920040</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5083,22 +4963,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>18330051920168</v>
+        <v>19330051920040</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5106,22 +4986,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920026</v>
+        <v>19330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5129,16 +5009,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920026</v>
+        <v>19330051920004</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5152,22 +5032,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920037</v>
+        <v>19330051920016</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5175,22 +5055,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920037</v>
+        <v>19330051920010</v>
       </c>
       <c r="B9" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5198,22 +5078,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920040</v>
+        <v>19330051920017</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5221,22 +5101,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920040</v>
+        <v>19330051920018</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5244,16 +5124,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920003</v>
+        <v>18330051920168</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -5267,16 +5147,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920004</v>
+        <v>19330051920026</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5290,16 +5170,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920016</v>
+        <v>19330051920024</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5313,22 +5193,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920012</v>
+        <v>19330051920038</v>
       </c>
       <c r="B15" t="s">
         <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5336,16 +5216,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920017</v>
+        <v>19330051920037</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5359,16 +5239,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920018</v>
+        <v>19330051920039</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5377,52 +5257,6 @@
         <v>59</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>18330061460390</v>
-      </c>
-      <c r="B18" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920038</v>
-      </c>
-      <c r="B19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -200,10 +200,10 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Ortega Valle Manuel</t>
@@ -1019,7 +1019,7 @@
         <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>7</v>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -1250,7 +1250,7 @@
         <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>10</v>
@@ -1327,7 +1327,7 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1481,7 +1481,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>10</v>
@@ -1558,7 +1558,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1635,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1712,7 +1712,7 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -1789,7 +1789,7 @@
         <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -1807,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1866,7 +1866,7 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>5</v>
@@ -1884,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -2020,7 +2020,7 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2097,7 +2097,7 @@
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -2174,7 +2174,7 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>10</v>
@@ -2251,7 +2251,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -2269,7 +2269,7 @@
         <v>6</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>7</v>
@@ -2423,7 +2423,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -2559,7 +2559,7 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>9</v>
@@ -2636,7 +2636,7 @@
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
         <v>9</v>
@@ -2654,7 +2654,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2713,7 +2713,7 @@
         <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -2731,7 +2731,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>6</v>
@@ -2790,7 +2790,7 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>9</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -3995,19 +3995,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G3">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4027,19 +4027,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="G4">
-        <v>15.79</v>
+        <v>13.16</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4862,7 +4862,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4894,19 +4894,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920034</v>
+        <v>19330051920014</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>60</v>
@@ -4917,16 +4917,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920034</v>
+        <v>19330051920014</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4940,22 +4940,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920040</v>
+        <v>19330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920040</v>
+        <v>19330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4986,22 +4986,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920003</v>
+        <v>19330051920040</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5009,22 +5009,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920004</v>
+        <v>19330051920040</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5032,16 +5032,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920016</v>
+        <v>19330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5055,22 +5055,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920010</v>
+        <v>19330051920004</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5078,16 +5078,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920017</v>
+        <v>19330051920016</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -5101,16 +5101,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920018</v>
+        <v>19330051920017</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5124,16 +5124,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920168</v>
+        <v>19330051920018</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -5147,16 +5147,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920026</v>
+        <v>18330051920168</v>
       </c>
       <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
         <v>85</v>
       </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5170,16 +5170,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920024</v>
+        <v>19330051920026</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -5193,16 +5193,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920038</v>
+        <v>19330051920024</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5216,16 +5216,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920037</v>
+        <v>19330051920038</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -5239,16 +5239,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920039</v>
+        <v>19330051920037</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -5257,6 +5257,29 @@
         <v>59</v>
       </c>
       <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920039</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEM - Estadisticos 20212.xlsx
+++ b/grupos/6AEM - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="159">
   <si>
     <t>Materia</t>
   </si>
@@ -197,19 +197,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
+    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
@@ -1031,7 +1031,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>6</v>
@@ -1108,7 +1108,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -1126,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1185,7 +1185,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1262,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1339,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
@@ -1404,7 +1404,7 @@
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1493,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1511,7 +1511,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1570,7 +1570,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1647,7 +1647,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1724,7 +1724,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1801,7 +1801,7 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1819,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1878,7 +1878,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1896,7 +1896,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -2032,7 +2032,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -2050,7 +2050,7 @@
         <v>9</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2109,7 +2109,7 @@
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2127,7 +2127,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2186,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2204,7 +2204,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2263,7 +2263,7 @@
         <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2281,7 +2281,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2328,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>5</v>
@@ -2340,7 +2340,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -2417,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2494,7 +2494,7 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2571,7 +2571,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2589,7 +2589,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2648,7 +2648,7 @@
         <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2666,7 +2666,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2725,7 +2725,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -2743,7 +2743,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2802,7 +2802,7 @@
         <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2820,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2867,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>9</v>
@@ -2879,13 +2879,13 @@
         <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2897,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2944,7 +2944,7 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>10</v>
@@ -2956,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>9</v>
@@ -3033,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3098,7 +3098,7 @@
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -3110,7 +3110,7 @@
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -3175,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>10</v>
@@ -3187,7 +3187,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3252,7 +3252,7 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>10</v>
@@ -3264,7 +3264,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>8</v>
@@ -3329,7 +3329,7 @@
         <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>5</v>
@@ -3341,13 +3341,13 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>5</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3359,7 +3359,7 @@
         <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3406,7 +3406,7 @@
         <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>6</v>
@@ -3418,13 +3418,13 @@
         <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>6</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35">
         <v>6</v>
@@ -3436,7 +3436,7 @@
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3483,7 +3483,7 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>10</v>
@@ -3495,7 +3495,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3560,7 +3560,7 @@
         <v>7</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>5</v>
@@ -3572,13 +3572,13 @@
         <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>6</v>
       </c>
       <c r="U37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>5</v>
@@ -3590,7 +3590,7 @@
         <v>5</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3637,7 +3637,7 @@
         <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3649,7 +3649,7 @@
         <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>6</v>
@@ -3667,7 +3667,7 @@
         <v>6</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3714,7 +3714,7 @@
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         <v>7</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
         <v>6</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3791,7 +3791,7 @@
         <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>6</v>
@@ -3803,7 +3803,7 @@
         <v>8</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>6</v>
@@ -3821,7 +3821,7 @@
         <v>6</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3868,7 +3868,7 @@
         <v>5</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P41">
         <v>5</v>
@@ -3880,13 +3880,13 @@
         <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T41">
         <v>5</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V41">
         <v>6</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -3963,19 +3963,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>52.63</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G2">
-        <v>47.37</v>
+        <v>15.79</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -3995,19 +3995,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="G3">
-        <v>15.79</v>
+        <v>13.16</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -4027,19 +4027,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="G4">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -4059,19 +4059,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>86.84</v>
+        <v>92.11</v>
       </c>
       <c r="G5">
-        <v>13.16</v>
+        <v>7.89</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -4103,7 +4103,7 @@
         <v>7.89</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4862,7 +4862,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4894,19 +4894,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920014</v>
+        <v>19330051920032</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>60</v>
@@ -4917,19 +4917,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920014</v>
+        <v>19330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>59</v>
@@ -4940,22 +4940,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920034</v>
+        <v>19330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4963,22 +4963,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920034</v>
+        <v>19330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4986,22 +4986,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920040</v>
+        <v>19330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5009,277 +5009,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920040</v>
+        <v>19330051920014</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920003</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920004</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920016</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920017</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920018</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D12" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>18330051920168</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920026</v>
-      </c>
-      <c r="B14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>144</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920024</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920038</v>
-      </c>
-      <c r="B16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920037</v>
-      </c>
-      <c r="B17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920039</v>
-      </c>
-      <c r="B18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>
